--- a/custer_org_employee.xlsx
+++ b/custer_org_employee.xlsx
@@ -31,7 +31,7 @@
     <t>语文</t>
   </si>
   <si>
-    <t>80</t>
+    <t>81</t>
   </si>
   <si>
     <t>李云龙</t>
@@ -408,9 +408,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2"/>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
+      <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
@@ -458,8 +456,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B3"/>
   </mergeCells>
 </worksheet>
 </file>
--- a/custer_org_employee.xlsx
+++ b/custer_org_employee.xlsx
@@ -408,7 +408,9 @@
     </row>
     <row r="3">
       <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
@@ -434,9 +436,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
         <v>9</v>
       </c>
@@ -458,7 +458,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A5:A6"/>
   </mergeCells>
 </worksheet>
 </file>